--- a/分析結果表(範例).xlsx
+++ b/分析結果表(範例).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gyzhu\Desktop\電腦小組\1150615研析試作區\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E198E6D-D58D-455E-BA9D-8C4BDC8750B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C56E92-0496-4BE7-8E30-A0E4B2723041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14370" yWindow="1140" windowWidth="13050" windowHeight="12330" xr2:uid="{4BB4B956-2790-4795-BE1E-941B17A37963}"/>
   </bookViews>

--- a/分析結果表(範例).xlsx
+++ b/分析結果表(範例).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gyzhu\Desktop\電腦小組\1150615研析試作區\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37C56E92-0496-4BE7-8E30-A0E4B2723041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9111FC-FB9E-4A31-BE00-35E5EF21431F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14370" yWindow="1140" windowWidth="13050" windowHeight="12330" xr2:uid="{4BB4B956-2790-4795-BE1E-941B17A37963}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4BB4B956-2790-4795-BE1E-941B17A37963}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
   <si>
     <t>種類</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -137,6 +137,10 @@
   </si>
   <si>
     <t>詳細情形</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二階段：核對會議紀錄</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -504,14 +508,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6FC2201-7A83-47E0-B197-638E9CB3EFA9}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="20.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="29.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -534,10 +539,13 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -548,7 +556,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -559,7 +567,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -567,7 +575,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -575,7 +583,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -583,7 +591,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -591,7 +599,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -599,7 +607,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -607,7 +615,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -615,7 +623,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -623,7 +631,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -631,7 +639,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -639,7 +647,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -647,7 +655,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -655,7 +663,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>25</v>
       </c>

--- a/分析結果表(範例).xlsx
+++ b/分析結果表(範例).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gyzhu\Desktop\電腦小組\1150615研析試作區\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD9111FC-FB9E-4A31-BE00-35E5EF21431F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D084B89-5DF2-4A57-970B-EECCABC91BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4BB4B956-2790-4795-BE1E-941B17A37963}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="31">
   <si>
     <t>種類</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -141,6 +141,10 @@
   </si>
   <si>
     <t>第二階段：核對會議紀錄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合計</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -508,15 +512,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6FC2201-7A83-47E0-B197-638E9CB3EFA9}">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="20.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.375" customWidth="1"/>
+    <col min="8" max="8" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -539,13 +544,16 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s">
         <v>29</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -556,7 +564,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -567,7 +575,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -575,7 +583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -583,7 +591,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -591,7 +599,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -599,7 +607,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -607,7 +615,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -615,7 +623,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -623,7 +631,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -631,7 +639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>25</v>
       </c>
@@ -639,7 +647,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -647,7 +655,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -655,7 +663,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -663,7 +671,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>25</v>
       </c>
